--- a/data/sites/sales/Marketing Campaigns/content-calendar-q3.xlsx
+++ b/data/sites/sales/Marketing Campaigns/content-calendar-q3.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Content Calendar - Q3</t>
+          <t>Content Calendar - Q3 - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,107 +651,2261 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 1 (Executive Summary &amp; Scope) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Case studies are prioritized from customers with the strongest measurable outcomes. Secondary control 1.2: Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total Cost of Ownership Webinar</t>
+          <t>Faster Onboarding Case Study</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Webinar</t>
+          <t>Case Study</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marcus Lee</t>
+          <t>Sofia Alvarez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Integration Best Practices Blog</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 10 (Cross-Functional Dependencies) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Webinar topics are selected based on top inbound content engagement themes. Secondary control 10.2: Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 11 (Continuous Improvement Roadmap) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Each asset has a designated distribution channel plan before publish date. Secondary control 11.2: Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: Underperforming content categories are reviewed and deprioritized quarterly. Secondary control 12.2: Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 2 (Architecture &amp; Process Flow) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Webinar topics are selected based on top inbound content engagement themes. Secondary control 2.2: Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 3 (Governance Standards &amp; Controls) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Each asset has a designated distribution channel plan before publish date. Secondary control 3.2: Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 4 (Operational KPIs &amp; Benchmarks) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: Underperforming content categories are reviewed and deprioritized quarterly. Secondary control 4.2: Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 5 (Roles, Responsibilities &amp; RACI) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Case studies are prioritized from customers with the strongest measurable outcomes. Secondary control 5.2: Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 6 (Standard Operating Procedures) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Webinar topics are selected based on top inbound content engagement themes. Secondary control 6.2: Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 7 (Risk Register &amp; Mitigations) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Each asset has a designated distribution channel plan before publish date. Secondary control 7.2: Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Each asset has a designated distribution channel plan before publish date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 8 (Quality Assurance &amp; Audits) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: Underperforming content categories are reviewed and deprioritized quarterly. Secondary control 8.2: Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content Calendar - Q3 - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 9 (Exception Handling &amp; Escalations) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Case studies are prioritized from customers with the strongest measurable outcomes. Secondary control 9.2: Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Publish Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faster Onboarding Case Study</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Study</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total Cost of Ownership Webinar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marcus Lee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Best Practices Blog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofia Alvarez</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/sales/Marketing Campaigns/content-calendar-q3.xlsx
+++ b/data/sites/sales/Marketing Campaigns/content-calendar-q3.xlsx
@@ -13,12 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Sign-off" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -220,96 +215,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -792,583 +697,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Content Calendar - Q3 - Section 10: Cross-Functional Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 10 (Cross-Functional Dependencies) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Documents upstream and downstream team dependencies and service-level commitments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 10.1: Webinar topics are selected based on top inbound content engagement themes. Secondary control 10.2: Each asset has a designated distribution channel plan before publish date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Cost of Ownership Webinar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Integration Best Practices Blog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 10 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Each asset has a designated distribution channel plan before publish date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 10 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Content Calendar - Q3 - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 11 (Continuous Improvement Roadmap) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: Each asset has a designated distribution channel plan before publish date. Secondary control 11.2: Underperforming content categories are reviewed and deprioritized quarterly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Cost of Ownership Webinar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Integration Best Practices Blog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Each asset has a designated distribution channel plan before publish date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Content Calendar - Q3 - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: Underperforming content categories are reviewed and deprioritized quarterly. Secondary control 12.2: Case studies are prioritized from customers with the strongest measurable outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Cost of Ownership Webinar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Integration Best Practices Blog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2350,7 +1678,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Content Calendar - Q3 - Section 7: Risk Register &amp; Mitigations</t>
+          <t>Content Calendar - Q3 - Section 7: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -2364,7 +1692,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 7 (Risk Register &amp; Mitigations) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 7 (Appendix, Lineage &amp; Sign-off) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -2522,390 +1850,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Content Calendar - Q3 - Section 8: Quality Assurance &amp; Audits</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 8 (Quality Assurance &amp; Audits) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 8.1: Underperforming content categories are reviewed and deprioritized quarterly. Secondary control 8.2: Case studies are prioritized from customers with the strongest measurable outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Cost of Ownership Webinar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Integration Best Practices Blog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 8 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Underperforming content categories are reviewed and deprioritized quarterly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 8 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Content Calendar - Q3 - Section 9: Exception Handling &amp; Escalations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing Knowledge Hub | Marketing Campaigns | Owner: Sofia Alvarez  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Editorial calendar tracking planned blog, webinar, and case study content with owner and publish date. Section 9 (Exception Handling &amp; Escalations) applies to Marketing Campaigns within Sales &amp; Marketing Knowledge Hub and is maintained by Sofia Alvarez. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 9.1: Case studies are prioritized from customers with the strongest measurable outcomes. Secondary control 9.2: Webinar topics are selected based on top inbound content engagement themes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Publish Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faster Onboarding Case Study</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Case Study</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Cost of Ownership Webinar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Webinar</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marcus Lee</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Integration Best Practices Blog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sofia Alvarez</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 9 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Case studies are prioritized from customers with the strongest measurable outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Webinar topics are selected based on top inbound content engagement themes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 9 review cadence is tracked by Sofia Alvarez under Marketing Campaigns governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>